--- a/artfynd/A 50618-2022 artfynd.xlsx
+++ b/artfynd/A 50618-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50618-2022 artfynd.xlsx
+++ b/artfynd/A 50618-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105374942</v>
+        <v>105374938</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>709619.7433507387</v>
+        <v>709683</v>
       </c>
       <c r="R2" t="n">
-        <v>6649997.408723488</v>
+        <v>6649935</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105374938</v>
+        <v>105374943</v>
       </c>
       <c r="B3" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>709683.649448899</v>
+        <v>709607</v>
       </c>
       <c r="R3" t="n">
-        <v>6649935.235964177</v>
+        <v>6649997</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,16 +872,11 @@
         <v>105374939</v>
       </c>
       <c r="B4" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>709667.8627803384</v>
+        <v>709668</v>
       </c>
       <c r="R4" t="n">
-        <v>6649974.020993395</v>
+        <v>6649974</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,50 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105374941</v>
+        <v>105374940</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stabby Gård, Upl</t>
+          <t>Stabby gård, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>709655.8913560032</v>
+        <v>709661</v>
       </c>
       <c r="R5" t="n">
-        <v>6649989.916996649</v>
+        <v>6649989</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105374940</v>
+        <v>105374941</v>
       </c>
       <c r="B6" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,34 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stabby gård, Upl</t>
+          <t>Stabby Gård, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>709660.9918450197</v>
+        <v>709656</v>
       </c>
       <c r="R6" t="n">
-        <v>6649988.699659328</v>
+        <v>6649990</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,6 +1157,103 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>105374942</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stabby gård, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>709620</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6649997</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-10-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-10-12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Karolin Ring</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50618-2022 artfynd.xlsx
+++ b/artfynd/A 50618-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105374938</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105374943</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105374939</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105374940</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105374941</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,8 +1284,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105374942</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>